--- a/docs/01_db/社員テーブル定義書.xlsx
+++ b/docs/01_db/社員テーブル定義書.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4458C5A-122A-4C58-991E-3A781BA5A09A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B28AAF2-A08F-4EE8-AC61-A8CDADF65B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{84575686-D333-47A9-97C0-193D95775C32}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>項番</t>
     <rPh sb="0" eb="2">
@@ -63,17 +63,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>name</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>氏名</t>
-    <rPh sb="0" eb="2">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>データ型</t>
     <rPh sb="3" eb="4">
       <t>ガタ</t>
@@ -81,10 +70,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>INT</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>NotNullの有無</t>
     <rPh sb="8" eb="10">
       <t>ウム</t>
@@ -106,10 +91,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>EmployeeID</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>社員ID</t>
     <rPh sb="0" eb="2">
       <t>シャイン</t>
@@ -117,10 +98,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>DepartmentID</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>部署ID</t>
     <rPh sb="0" eb="2">
       <t>ブショ</t>
@@ -135,13 +112,36 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>String</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>テーブル定義書</t>
     <rPh sb="4" eb="7">
       <t>テイギショ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Employee_ID</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Department_ID</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Employee_Name</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SMALLINT(4)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>VARCHAR(30)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>社員名</t>
+    <rPh sb="0" eb="3">
+      <t>シャインメイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -578,7 +578,8 @@
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="3" width="10.08203125" style="1" customWidth="1"/>
-    <col min="4" max="5" width="13.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.75" style="1" customWidth="1"/>
     <col min="6" max="6" width="23.83203125" style="1" customWidth="1"/>
     <col min="7" max="9" width="17.33203125" style="1" customWidth="1"/>
     <col min="10" max="11" width="21.83203125" style="1" customWidth="1"/>
@@ -587,7 +588,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="6" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -602,10 +603,10 @@
     <row r="3" spans="1:7" ht="24.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3"/>
       <c r="D3" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G3" s="5"/>
     </row>
@@ -617,7 +618,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>3</v>
@@ -626,10 +627,10 @@
         <v>4</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -639,17 +640,15 @@
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>12</v>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>2</v>
@@ -662,10 +661,10 @@
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>17</v>
@@ -686,10 +685,10 @@
         <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>2</v>
